--- a/data/trans_dic/P25A$molestias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,13</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,09</t>
+          <t>0,0; 32,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,49</t>
+          <t>0,0; 23,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,99</t>
+          <t>0,0; 30,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,02</t>
+          <t>0,0; 20,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 19,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,84</t>
+          <t>0,0; 22,03</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 25,28</t>
+          <t>4,5; 25,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 21,02</t>
+          <t>5,12; 21,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,03</t>
+          <t>0,0; 17,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 20,92</t>
+          <t>4,67; 20,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,09</t>
+          <t>1,17; 11,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,35</t>
+          <t>1,54; 12,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 17,59</t>
+          <t>6,27; 17,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,43</t>
+          <t>3,76; 12,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,41</t>
+          <t>1,77; 12,08</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 21,54</t>
+          <t>6,49; 20,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 12,78</t>
+          <t>3,44; 13,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 26,58</t>
+          <t>8,15; 25,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 30,0</t>
+          <t>10,91; 31,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 13,84</t>
+          <t>3,84; 13,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,94; 29,7</t>
+          <t>11,56; 28,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,5</t>
+          <t>10,59; 22,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 11,53</t>
+          <t>4,47; 11,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 24,15</t>
+          <t>11,56; 23,89</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 29,64</t>
+          <t>14,23; 29,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 12,53</t>
+          <t>3,84; 12,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 28,36</t>
+          <t>12,64; 28,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 26,76</t>
+          <t>8,09; 27,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 15,79</t>
+          <t>3,49; 15,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 19,57</t>
+          <t>5,79; 20,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,85; 25,59</t>
+          <t>14,29; 26,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 11,76</t>
+          <t>4,82; 11,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 21,48</t>
+          <t>10,83; 21,82</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 26,84</t>
+          <t>12,42; 26,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 17,66</t>
+          <t>6,76; 18,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 21,02</t>
+          <t>7,65; 21,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 53,73</t>
+          <t>11,25; 57,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 31,13</t>
+          <t>8,34; 33,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 32,21</t>
+          <t>9,55; 31,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 28,13</t>
+          <t>14,1; 27,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 20,08</t>
+          <t>9,01; 18,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 21,61</t>
+          <t>10,05; 20,46</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,49; 29,92</t>
+          <t>15,38; 29,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 21,65</t>
+          <t>10,37; 21,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 24,38</t>
+          <t>11,12; 24,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,24</t>
+          <t>0,0; 55,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,61; 28,67</t>
+          <t>3,6; 31,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,35; 27,55</t>
+          <t>13,91; 26,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,29; 21,62</t>
+          <t>10,14; 22,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 22,65</t>
+          <t>10,56; 22,86</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1338,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,94; 30,33</t>
+          <t>14,81; 31,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 19,01</t>
+          <t>6,22; 18,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,5; 26,27</t>
+          <t>13,2; 26,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,93</t>
+          <t>0,0; 65,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,92; 28,96</t>
+          <t>14,1; 28,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 17,96</t>
+          <t>6,56; 18,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 27,68</t>
+          <t>13,75; 26,84</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,93</t>
+          <t>15,98; 22,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,2</t>
+          <t>8,56; 12,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,28</t>
+          <t>12,97; 19,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,27</t>
+          <t>10,33; 18,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,83</t>
+          <t>6,18; 12,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,63</t>
+          <t>10,23; 17,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,38</t>
+          <t>15,15; 20,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,93</t>
+          <t>8,35; 12,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,37</t>
+          <t>12,52; 17,33</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4439</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5573</t>
+          <t>0; 5044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5094</t>
+          <t>0; 4498</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5113</t>
+          <t>0; 5070</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6152</t>
+          <t>0; 5451</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6166</t>
+          <t>0; 6901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6186</t>
+          <t>0; 5715</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1787; 9974</t>
+          <t>1775; 10147</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3165; 15291</t>
+          <t>3722; 15592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8273</t>
+          <t>0; 8620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3016; 14655</t>
+          <t>3272; 14621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>993; 9187</t>
+          <t>969; 9230</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>894; 6580</t>
+          <t>892; 7412</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6838; 19268</t>
+          <t>6862; 19639</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5979; 20897</t>
+          <t>5845; 19858</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1854; 12158</t>
+          <t>1882; 12869</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5732; 18296</t>
+          <t>5514; 17020</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3737; 14361</t>
+          <t>3865; 15093</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6371; 19754</t>
+          <t>6058; 19018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7383; 19881</t>
+          <t>7232; 20808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4674; 17177</t>
+          <t>4771; 17226</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10502; 26115</t>
+          <t>10169; 25146</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15711; 32515</t>
+          <t>16021; 33474</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9752; 27253</t>
+          <t>10573; 27229</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19285; 39190</t>
+          <t>18751; 38758</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18406; 37212</t>
+          <t>17869; 37140</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6964; 21294</t>
+          <t>6530; 21377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13224; 30678</t>
+          <t>13678; 30426</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4867; 15720</t>
+          <t>4755; 16156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3098; 14459</t>
+          <t>3199; 14261</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5259; 17271</t>
+          <t>5109; 17695</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25521; 47164</t>
+          <t>26343; 49276</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12034; 30748</t>
+          <t>12600; 30299</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20352; 42198</t>
+          <t>21268; 42862</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16438; 34383</t>
+          <t>15914; 33353</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8588; 24767</t>
+          <t>9486; 25729</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10582; 27952</t>
+          <t>10176; 27940</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1956; 9370</t>
+          <t>1961; 9977</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4200; 16114</t>
+          <t>4316; 17521</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5534; 18336</t>
+          <t>5436; 18184</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21112; 40941</t>
+          <t>20526; 39992</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16217; 38560</t>
+          <t>17300; 36074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19885; 41044</t>
+          <t>19083; 38856</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18886; 36477</t>
+          <t>18747; 36094</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17229; 35190</t>
+          <t>16858; 35189</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13722; 30041</t>
+          <t>13696; 30344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1707</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5974</t>
+          <t>0; 5912</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>930; 7386</t>
+          <t>929; 8060</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19437; 37313</t>
+          <t>18837; 36049</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17813; 37435</t>
+          <t>17563; 38099</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16316; 33738</t>
+          <t>15726; 34055</t>
         </is>
       </c>
     </row>
@@ -2728,27 +2728,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16928; 34359</t>
+          <t>16776; 36115</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8624; 26902</t>
+          <t>8796; 26303</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14675; 28566</t>
+          <t>14347; 28864</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4225</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17051; 35486</t>
+          <t>17282; 35055</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9530; 26554</t>
+          <t>9699; 27277</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15560; 30781</t>
+          <t>15292; 29855</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>98278; 136992</t>
+          <t>99837; 137503</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69519; 107720</t>
+          <t>69852; 104258</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79415; 116761</t>
+          <t>78537; 115709</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26066; 48311</t>
+          <t>25904; 47492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24537; 49587</t>
+          <t>23883; 48479</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34529; 59203</t>
+          <t>34350; 59179</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>133501; 178395</t>
+          <t>132571; 176070</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100155; 143504</t>
+          <t>100440; 145462</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>119428; 163504</t>
+          <t>117851; 163134</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$molestias-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Edad-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,45</t>
+          <t>0,0; 25,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,66</t>
+          <t>0,0; 37,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,39</t>
+          <t>0,0; 21,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,73</t>
+          <t>0,0; 30,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,39</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,16</t>
+          <t>0,0; 16,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,03</t>
+          <t>0,0; 19,83</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 25,72</t>
+          <t>4,49; 23,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 21,44</t>
+          <t>5,03; 22,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,74</t>
+          <t>0,0; 18,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 20,87</t>
+          <t>4,31; 20,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,14</t>
+          <t>1,2; 12,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,79</t>
+          <t>1,54; 12,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 17,93</t>
+          <t>6,15; 17,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,76</t>
+          <t>3,9; 13,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 12,08</t>
+          <t>1,77; 12,91</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 20,03</t>
+          <t>6,33; 20,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 13,43</t>
+          <t>3,38; 12,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 25,59</t>
+          <t>8,15; 26,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 31,4</t>
+          <t>11,64; 30,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,88</t>
+          <t>3,83; 14,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 28,6</t>
+          <t>11,91; 28,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,59; 22,14</t>
+          <t>10,63; 22,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,52</t>
+          <t>4,36; 11,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 23,89</t>
+          <t>11,79; 23,95</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 29,58</t>
+          <t>14,52; 29,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,58</t>
+          <t>3,83; 12,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 28,12</t>
+          <t>12,78; 28,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 27,5</t>
+          <t>8,08; 26,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 15,57</t>
+          <t>3,57; 15,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 20,06</t>
+          <t>6,08; 20,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 26,74</t>
+          <t>13,36; 25,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,59</t>
+          <t>4,71; 11,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 21,82</t>
+          <t>10,61; 21,81</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 26,03</t>
+          <t>13,06; 26,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 18,35</t>
+          <t>6,54; 19,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 21,01</t>
+          <t>7,82; 20,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 57,21</t>
+          <t>11,51; 59,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 33,85</t>
+          <t>8,23; 34,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 31,95</t>
+          <t>9,39; 33,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,1; 27,47</t>
+          <t>14,04; 27,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 18,79</t>
+          <t>8,41; 19,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 20,46</t>
+          <t>9,99; 20,98</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 29,61</t>
+          <t>14,99; 29,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 21,65</t>
+          <t>10,08; 21,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,12; 24,63</t>
+          <t>11,45; 24,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,27 +1248,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,65</t>
+          <t>0,0; 56,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 31,29</t>
+          <t>3,61; 30,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,91; 26,62</t>
+          <t>13,73; 26,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 22,0</t>
+          <t>10,2; 21,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,86</t>
+          <t>10,59; 22,66</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,81; 31,88</t>
+          <t>15,37; 31,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 18,59</t>
+          <t>6,71; 19,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,2; 26,55</t>
+          <t>12,98; 26,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,67</t>
+          <t>0,0; 66,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,1; 28,61</t>
+          <t>13,37; 28,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 18,44</t>
+          <t>6,76; 18,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,75; 26,84</t>
+          <t>13,47; 27,35</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,98; 22,02</t>
+          <t>15,9; 22,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,78</t>
+          <t>8,59; 12,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,11</t>
+          <t>12,8; 19,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,94</t>
+          <t>10,68; 19,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,54</t>
+          <t>5,96; 12,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,23; 17,62</t>
+          <t>10,05; 17,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,15; 20,12</t>
+          <t>15,24; 20,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,1</t>
+          <t>8,31; 11,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,52; 17,33</t>
+          <t>12,82; 17,48</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 4278</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1765,32 +1765,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5044</t>
+          <t>0; 5817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4498</t>
+          <t>0; 4103</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5070</t>
+          <t>0; 5065</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5451</t>
+          <t>0; 5525</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6901</t>
+          <t>0; 6061</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5715</t>
+          <t>0; 5146</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1775; 10147</t>
+          <t>1773; 9079</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3722; 15592</t>
+          <t>3657; 16146</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8620</t>
+          <t>0; 8796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3272; 14621</t>
+          <t>3021; 14047</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>969; 9230</t>
+          <t>993; 9963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>892; 7412</t>
+          <t>891; 7452</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6862; 19639</t>
+          <t>6734; 19695</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5845; 19858</t>
+          <t>6065; 21258</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1882; 12869</t>
+          <t>1881; 13760</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5514; 17020</t>
+          <t>5376; 17072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3865; 15093</t>
+          <t>3792; 14033</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6058; 19018</t>
+          <t>6054; 19353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7232; 20808</t>
+          <t>7713; 20375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4771; 17226</t>
+          <t>4748; 17740</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10169; 25146</t>
+          <t>10477; 25487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16021; 33474</t>
+          <t>16077; 33269</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10573; 27229</t>
+          <t>10299; 27494</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18751; 38758</t>
+          <t>19124; 38859</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17869; 37140</t>
+          <t>18235; 37294</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6530; 21377</t>
+          <t>6500; 20427</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13678; 30426</t>
+          <t>13822; 31168</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4755; 16156</t>
+          <t>4746; 15530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3199; 14261</t>
+          <t>3265; 14357</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5109; 17695</t>
+          <t>5364; 18133</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26343; 49276</t>
+          <t>24620; 47631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12600; 30299</t>
+          <t>12323; 29582</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21268; 42862</t>
+          <t>20847; 42837</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15914; 33353</t>
+          <t>16728; 33409</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9486; 25729</t>
+          <t>9169; 26684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10176; 27940</t>
+          <t>10397; 27590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1961; 9977</t>
+          <t>2007; 10292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4316; 17521</t>
+          <t>4261; 17814</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5436; 18184</t>
+          <t>5346; 18819</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20526; 39992</t>
+          <t>20443; 39517</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17300; 36074</t>
+          <t>16156; 37665</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19083; 38856</t>
+          <t>18978; 39850</t>
         </is>
       </c>
     </row>
@@ -2565,17 +2565,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18747; 36094</t>
+          <t>18274; 35977</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16858; 35189</t>
+          <t>16383; 34776</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13696; 30344</t>
+          <t>14112; 29691</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2585,27 +2585,27 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5912</t>
+          <t>0; 6018</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>929; 8060</t>
+          <t>929; 7803</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18837; 36049</t>
+          <t>18593; 36195</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17563; 38099</t>
+          <t>17658; 37925</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15726; 34055</t>
+          <t>15771; 33763</t>
         </is>
       </c>
     </row>
@@ -2728,17 +2728,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16776; 36115</t>
+          <t>17418; 35812</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8796; 26303</t>
+          <t>9494; 27854</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14347; 28864</t>
+          <t>14117; 28585</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 4260</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17282; 35055</t>
+          <t>16385; 34975</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9699; 27277</t>
+          <t>9993; 27899</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15292; 29855</t>
+          <t>14982; 30415</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>99837; 137503</t>
+          <t>99299; 139156</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>69852; 104258</t>
+          <t>70060; 105400</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78537; 115709</t>
+          <t>77530; 115363</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25904; 47492</t>
+          <t>26767; 48486</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23883; 48479</t>
+          <t>23031; 48870</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34350; 59179</t>
+          <t>33752; 58845</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>132571; 176070</t>
+          <t>133355; 177937</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>100440; 145462</t>
+          <t>99887; 144016</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>117851; 163134</t>
+          <t>120630; 164544</t>
         </is>
       </c>
     </row>
